--- a/artfynd/A 57266-2020 artfynd.xlsx
+++ b/artfynd/A 57266-2020 artfynd.xlsx
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118360877</v>
+        <v>118360895</v>
       </c>
       <c r="B10" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,41 +1602,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579429</v>
+        <v>579560</v>
       </c>
       <c r="R10" t="n">
-        <v>6589632</v>
+        <v>6589664</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1666,9 +1667,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118360895</v>
+        <v>118360877</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,42 +1719,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579560</v>
+        <v>579429</v>
       </c>
       <c r="R11" t="n">
-        <v>6589664</v>
+        <v>6589632</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1773,19 +1783,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 57266-2020 artfynd.xlsx
+++ b/artfynd/A 57266-2020 artfynd.xlsx
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118360895</v>
+        <v>118360877</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,42 +1602,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579560</v>
+        <v>579429</v>
       </c>
       <c r="R10" t="n">
-        <v>6589664</v>
+        <v>6589632</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,19 +1666,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118360877</v>
+        <v>118360895</v>
       </c>
       <c r="B11" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,41 +1708,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579429</v>
+        <v>579560</v>
       </c>
       <c r="R11" t="n">
-        <v>6589632</v>
+        <v>6589664</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1783,9 +1773,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 57266-2020 artfynd.xlsx
+++ b/artfynd/A 57266-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118360890</v>
+        <v>118360895</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579394</v>
+        <v>579560</v>
       </c>
       <c r="R2" t="n">
-        <v>6589702</v>
+        <v>6589664</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118360893</v>
+        <v>118360886</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -827,19 +827,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579547</v>
+        <v>579484</v>
       </c>
       <c r="R3" t="n">
-        <v>6589667</v>
+        <v>6589691</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118360897</v>
+        <v>118360890</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -944,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>81</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579324</v>
+        <v>579394</v>
       </c>
       <c r="R4" t="n">
-        <v>6589693</v>
+        <v>6589702</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,9 +990,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118360889</v>
+        <v>118360893</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1051,7 +1065,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579339</v>
+        <v>579547</v>
       </c>
       <c r="R5" t="n">
-        <v>6589611</v>
+        <v>6589667</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118360892</v>
+        <v>118360887</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1168,7 +1182,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>108</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579329</v>
+        <v>579336</v>
       </c>
       <c r="R6" t="n">
-        <v>6589607</v>
+        <v>6589703</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,19 +1224,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118360886</v>
+        <v>118360902</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,46 +1266,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579484</v>
+        <v>579251</v>
       </c>
       <c r="R7" t="n">
-        <v>6589691</v>
+        <v>6589575</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,28 +1327,17 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1371,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118360875</v>
+        <v>118360877</v>
       </c>
       <c r="B8" t="n">
-        <v>90504</v>
+        <v>90524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,34 +1372,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579482</v>
+        <v>579429</v>
       </c>
       <c r="R8" t="n">
-        <v>6589685</v>
+        <v>6589632</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,6 +1443,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1473,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118360894</v>
+        <v>118360892</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1508,7 +1497,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>47</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1517,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579433</v>
+        <v>579329</v>
       </c>
       <c r="R9" t="n">
-        <v>6589636</v>
+        <v>6589607</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118360877</v>
+        <v>118360875</v>
       </c>
       <c r="B10" t="n">
-        <v>90524</v>
+        <v>90504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,37 +1595,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579429</v>
+        <v>579482</v>
       </c>
       <c r="R10" t="n">
-        <v>6589632</v>
+        <v>6589685</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1677,7 +1663,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118360895</v>
+        <v>118360894</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1740,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579560</v>
+        <v>579433</v>
       </c>
       <c r="R11" t="n">
-        <v>6589664</v>
+        <v>6589636</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1775,7 +1760,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1770,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,7 +1798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118360887</v>
+        <v>118360889</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1848,7 +1833,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1857,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579336</v>
+        <v>579339</v>
       </c>
       <c r="R12" t="n">
-        <v>6589703</v>
+        <v>6589611</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1890,9 +1875,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118360902</v>
+        <v>118360896</v>
       </c>
       <c r="B13" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,38 +1927,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579251</v>
+        <v>579384</v>
       </c>
       <c r="R13" t="n">
-        <v>6589575</v>
+        <v>6589657</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1993,17 +1992,28 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2022,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118360896</v>
+        <v>118360897</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2057,7 +2067,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2066,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579384</v>
+        <v>579324</v>
       </c>
       <c r="R14" t="n">
-        <v>6589657</v>
+        <v>6589693</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2099,19 +2109,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 57266-2020 artfynd.xlsx
+++ b/artfynd/A 57266-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118360895</v>
+        <v>118360887</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>108</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579560</v>
+        <v>579336</v>
       </c>
       <c r="R2" t="n">
-        <v>6589664</v>
+        <v>6589703</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,19 +752,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118360886</v>
+        <v>118360896</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -827,23 +817,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579484</v>
+        <v>579384</v>
       </c>
       <c r="R3" t="n">
-        <v>6589691</v>
+        <v>6589657</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118360890</v>
+        <v>118360902</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,42 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579394</v>
+        <v>579251</v>
       </c>
       <c r="R4" t="n">
-        <v>6589702</v>
+        <v>6589575</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,28 +972,17 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118360893</v>
+        <v>118360897</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1065,7 +1036,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579547</v>
+        <v>579324</v>
       </c>
       <c r="R5" t="n">
-        <v>6589667</v>
+        <v>6589693</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,19 +1078,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118360887</v>
+        <v>118360894</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1182,7 +1143,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1191,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579336</v>
+        <v>579433</v>
       </c>
       <c r="R6" t="n">
-        <v>6589703</v>
+        <v>6589636</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,9 +1185,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118360902</v>
+        <v>118360893</v>
       </c>
       <c r="B7" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,38 +1237,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579251</v>
+        <v>579547</v>
       </c>
       <c r="R7" t="n">
-        <v>6589575</v>
+        <v>6589667</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1327,17 +1302,28 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1356,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118360877</v>
+        <v>118360892</v>
       </c>
       <c r="B8" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,41 +1354,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579429</v>
+        <v>579329</v>
       </c>
       <c r="R8" t="n">
-        <v>6589632</v>
+        <v>6589607</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,9 +1419,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118360892</v>
+        <v>118360890</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1497,7 +1494,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>81</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1506,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579329</v>
+        <v>579394</v>
       </c>
       <c r="R9" t="n">
-        <v>6589607</v>
+        <v>6589702</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1541,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118360875</v>
+        <v>118360886</v>
       </c>
       <c r="B10" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,38 +1588,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579482</v>
+        <v>579484</v>
       </c>
       <c r="R10" t="n">
-        <v>6589685</v>
+        <v>6589691</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1652,17 +1657,28 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118360894</v>
+        <v>118360877</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,42 +1709,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579433</v>
+        <v>579429</v>
       </c>
       <c r="R11" t="n">
-        <v>6589636</v>
+        <v>6589632</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1758,19 +1773,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118360896</v>
+        <v>118360875</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,42 +1932,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579384</v>
+        <v>579482</v>
       </c>
       <c r="R13" t="n">
-        <v>6589657</v>
+        <v>6589685</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1992,28 +1993,17 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2032,7 +2022,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118360897</v>
+        <v>118360895</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2067,7 +2057,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579324</v>
+        <v>579560</v>
       </c>
       <c r="R14" t="n">
-        <v>6589693</v>
+        <v>6589664</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2109,9 +2099,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 57266-2020 artfynd.xlsx
+++ b/artfynd/A 57266-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118360887</v>
+        <v>118360897</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579336</v>
+        <v>579324</v>
       </c>
       <c r="R2" t="n">
-        <v>6589703</v>
+        <v>6589693</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118360896</v>
+        <v>118360889</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579384</v>
+        <v>579339</v>
       </c>
       <c r="R3" t="n">
-        <v>6589657</v>
+        <v>6589611</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118360902</v>
+        <v>118360894</v>
       </c>
       <c r="B4" t="n">
-        <v>94620</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579251</v>
+        <v>579433</v>
       </c>
       <c r="R4" t="n">
-        <v>6589575</v>
+        <v>6589636</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,17 +976,28 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118360897</v>
+        <v>118360896</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579324</v>
+        <v>579384</v>
       </c>
       <c r="R5" t="n">
-        <v>6589693</v>
+        <v>6589657</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,9 +1093,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118360894</v>
+        <v>118360875</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,42 +1145,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579433</v>
+        <v>579482</v>
       </c>
       <c r="R6" t="n">
-        <v>6589636</v>
+        <v>6589685</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,28 +1206,17 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1225,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118360893</v>
+        <v>118360892</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,7 +1270,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>47</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1269,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579547</v>
+        <v>579329</v>
       </c>
       <c r="R7" t="n">
-        <v>6589667</v>
+        <v>6589607</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118360892</v>
+        <v>118360890</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,7 +1387,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>81</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1386,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579329</v>
+        <v>579394</v>
       </c>
       <c r="R8" t="n">
-        <v>6589607</v>
+        <v>6589702</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118360890</v>
+        <v>118360902</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>94627</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,42 +1481,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579394</v>
+        <v>579251</v>
       </c>
       <c r="R9" t="n">
-        <v>6589702</v>
+        <v>6589575</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1536,28 +1542,17 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118360886</v>
+        <v>118360895</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,23 +1606,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579484</v>
+        <v>579560</v>
       </c>
       <c r="R10" t="n">
-        <v>6589691</v>
+        <v>6589664</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,7 +1691,7 @@
         <v>118360877</v>
       </c>
       <c r="B11" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118360889</v>
+        <v>118360886</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,19 +1829,23 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579339</v>
+        <v>579484</v>
       </c>
       <c r="R12" t="n">
-        <v>6589611</v>
+        <v>6589691</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118360875</v>
+        <v>118360893</v>
       </c>
       <c r="B13" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,38 +1927,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579482</v>
+        <v>579547</v>
       </c>
       <c r="R13" t="n">
-        <v>6589685</v>
+        <v>6589667</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1993,17 +1992,28 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2022,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118360895</v>
+        <v>118360887</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,7 +2067,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>108</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2066,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579560</v>
+        <v>579336</v>
       </c>
       <c r="R14" t="n">
-        <v>6589664</v>
+        <v>6589703</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2099,19 +2109,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 57266-2020 artfynd.xlsx
+++ b/artfynd/A 57266-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118360897</v>
+        <v>118360893</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579324</v>
+        <v>579547</v>
       </c>
       <c r="R2" t="n">
-        <v>6589693</v>
+        <v>6589667</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,9 +752,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118360889</v>
+        <v>118360902</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>94627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579339</v>
+        <v>579251</v>
       </c>
       <c r="R3" t="n">
-        <v>6589611</v>
+        <v>6589575</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,28 +865,17 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118360896</v>
+        <v>118360895</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1051,7 +1046,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579384</v>
+        <v>579560</v>
       </c>
       <c r="R5" t="n">
-        <v>6589657</v>
+        <v>6589664</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118360875</v>
+        <v>118360897</v>
       </c>
       <c r="B6" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,38 +1140,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579482</v>
+        <v>579324</v>
       </c>
       <c r="R6" t="n">
-        <v>6589685</v>
+        <v>6589693</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,6 +1216,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118360892</v>
+        <v>118360889</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579329</v>
+        <v>579339</v>
       </c>
       <c r="R7" t="n">
-        <v>6589607</v>
+        <v>6589611</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118360890</v>
+        <v>118360896</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579394</v>
+        <v>579384</v>
       </c>
       <c r="R8" t="n">
-        <v>6589702</v>
+        <v>6589657</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118360902</v>
+        <v>118360890</v>
       </c>
       <c r="B9" t="n">
-        <v>94627</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,38 +1481,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579251</v>
+        <v>579394</v>
       </c>
       <c r="R9" t="n">
-        <v>6589575</v>
+        <v>6589702</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,17 +1546,28 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118360895</v>
+        <v>118360886</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1606,19 +1621,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579560</v>
+        <v>579484</v>
       </c>
       <c r="R10" t="n">
-        <v>6589664</v>
+        <v>6589691</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118360877</v>
+        <v>118360875</v>
       </c>
       <c r="B11" t="n">
-        <v>90531</v>
+        <v>90511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,37 +1723,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörkret, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579429</v>
+        <v>579482</v>
       </c>
       <c r="R11" t="n">
-        <v>6589632</v>
+        <v>6589685</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1775,7 +1791,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1794,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118360886</v>
+        <v>118360877</v>
       </c>
       <c r="B12" t="n">
-        <v>97853</v>
+        <v>90531</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,35 +1821,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1842,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579484</v>
+        <v>579429</v>
       </c>
       <c r="R12" t="n">
-        <v>6589691</v>
+        <v>6589632</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,19 +1885,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,7 +1915,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118360893</v>
+        <v>118360887</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>108</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579547</v>
+        <v>579336</v>
       </c>
       <c r="R13" t="n">
-        <v>6589667</v>
+        <v>6589703</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1992,19 +1992,9 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,7 +2022,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118360887</v>
+        <v>118360892</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2067,7 +2057,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>47</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579336</v>
+        <v>579329</v>
       </c>
       <c r="R14" t="n">
-        <v>6589703</v>
+        <v>6589607</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2109,9 +2099,19 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
